--- a/data/trans_camb/IP1013-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,32</t>
+          <t>-0,98; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,71</t>
+          <t>-0,76; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,45</t>
+          <t>-0,64; 0,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,64</t>
+          <t>-0,62; 0,63</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,99</t>
+          <t>0,35; 2,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,55</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,6</t>
+          <t>-0,27; 0,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,52</t>
+          <t>-0,29; 0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,54</t>
+          <t>-0,1; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 779,25</t>
+          <t>-69,36; 1067,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,31</t>
+          <t>-0,86; 1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,63</t>
+          <t>-0,74; 1,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,46</t>
+          <t>-0,64; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,63</t>
+          <t>-0,64; 0,62</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,98</t>
+          <t>0,35; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,18; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,52</t>
+          <t>-0,27; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,61</t>
+          <t>-0,1; 0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,56; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,43</t>
+          <t>-0,09; 0,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,24</t>
+          <t>-0,22; 0,25</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 1067,2</t>
+          <t>-66,5; inf</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,41</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,5</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-0,75; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-0,76; 1,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,47</t>
+          <t>-0,65; 0,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,62</t>
+          <t>-0,63; 0,64</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>20,93%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>40,51%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,35; 2,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,53</t>
+          <t>0,18; 1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,6</t>
+          <t>-0,11; 0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,56</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,54</t>
+          <t>-0,26; 0,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,0</t>
+          <t>-0,27; 0,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,43</t>
+          <t>-0,1; 0,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,25</t>
+          <t>-0,23; 0,24</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>183,98%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>58,24%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>58,61%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>183,98%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,5; inf</t>
+          <t>-79,12; 779,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
